--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126457812</v>
+        <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>58209</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102980</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495654</v>
+        <v>495734</v>
       </c>
       <c r="R2" t="n">
-        <v>6719285</v>
+        <v>6719209</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,38 +795,38 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126457812</t>
+          <t>https://artportalen.se/Sighting/136734963</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126369086</v>
+        <v>126457812</v>
       </c>
       <c r="B3" t="n">
-        <v>58463</v>
+        <v>58209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>102980</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495655</v>
+        <v>495654</v>
       </c>
       <c r="R3" t="n">
-        <v>6719196</v>
+        <v>6719285</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,59 +897,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126369086</t>
+          <t>https://artportalen.se/Sighting/126457812</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134516427</v>
+        <v>126369086</v>
       </c>
       <c r="B4" t="n">
-        <v>58410</v>
+        <v>58463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495640</v>
+        <v>495655</v>
       </c>
       <c r="R4" t="n">
-        <v>6719238</v>
+        <v>6719196</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,13 +999,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134516427</t>
+          <t>https://artportalen.se/Sighting/126369086</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134811381</v>
+        <v>134516427</v>
       </c>
       <c r="B5" t="n">
         <v>58410</v>
@@ -1041,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495654</v>
+        <v>495640</v>
       </c>
       <c r="R5" t="n">
-        <v>6719285</v>
+        <v>6719238</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1075,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,54 +1116,59 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134811381</t>
+          <t>https://artportalen.se/Sighting/134516427</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126388887</v>
+        <v>134811381</v>
       </c>
       <c r="B6" t="n">
-        <v>58327</v>
+        <v>58410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495728</v>
+        <v>495654</v>
       </c>
       <c r="R6" t="n">
-        <v>6719297</v>
+        <v>6719285</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,12 +1192,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,16 +1233,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126388887</t>
+          <t>https://artportalen.se/Sighting/134811381</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126388902</v>
+        <v>126388887</v>
       </c>
       <c r="B7" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R7" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,53 +1335,41 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126388902</t>
+          <t>https://artportalen.se/Sighting/126388887</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126487035</v>
+        <v>126388902</v>
       </c>
       <c r="B8" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1399,22 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,16 +1437,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487035</t>
+          <t>https://artportalen.se/Sighting/126388902</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134493111</v>
+        <v>126487035</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,25 +1471,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495728</v>
+        <v>495654</v>
       </c>
       <c r="R9" t="n">
-        <v>6719297</v>
+        <v>6719285</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,22 +1520,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,44 +1561,44 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493111</t>
+          <t>https://artportalen.se/Sighting/126487035</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135251208</v>
+        <v>134493111</v>
       </c>
       <c r="B10" t="n">
         <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1603,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495650</v>
+        <v>495728</v>
       </c>
       <c r="R10" t="n">
-        <v>6719267</v>
+        <v>6719297</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,22 +1637,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,16 +1678,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135251208</t>
+          <t>https://artportalen.se/Sighting/134493111</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126522050</v>
+        <v>135251208</v>
       </c>
       <c r="B11" t="n">
-        <v>58636</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,16 +1695,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>103023</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1709,19 +1713,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495654</v>
+        <v>495650</v>
       </c>
       <c r="R11" t="n">
-        <v>6719285</v>
+        <v>6719267</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,22 +1754,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,13 +1795,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126522050</t>
+          <t>https://artportalen.se/Sighting/135251208</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128412408</v>
+        <v>126522050</v>
       </c>
       <c r="B12" t="n">
         <v>58636</v>
@@ -1827,13 +1836,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495650</v>
+        <v>495654</v>
       </c>
       <c r="R12" t="n">
-        <v>6719267</v>
+        <v>6719285</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,22 +1866,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,16 +1907,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128412408</t>
+          <t>https://artportalen.se/Sighting/126522050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133065918</v>
+        <v>128412408</v>
       </c>
       <c r="B13" t="n">
-        <v>58671</v>
+        <v>58636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,16 +1924,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1933,11 +1942,6 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1974,12 +1978,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,22 +2013,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Stina Dalmalm</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133065918</t>
+          <t>https://artportalen.se/Sighting/128412408</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128402178</v>
+        <v>133065918</v>
       </c>
       <c r="B14" t="n">
-        <v>58085</v>
+        <v>58671</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,37 +2036,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205976</v>
+        <v>103057</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R14" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2076,22 +2095,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,44 +2120,44 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Stina Dalmalm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128402178</t>
+          <t>https://artportalen.se/Sighting/133065918</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127520634</v>
+        <v>128402178</v>
       </c>
       <c r="B15" t="n">
-        <v>56837</v>
+        <v>58085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206002</v>
+        <v>205976</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,13 +2167,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495650</v>
+        <v>495728</v>
       </c>
       <c r="R15" t="n">
-        <v>6719267</v>
+        <v>6719297</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,12 +2197,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,64 +2238,54 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127520634</t>
+          <t>https://artportalen.se/Sighting/128402178</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111173602</v>
+        <v>127520634</v>
       </c>
       <c r="B16" t="n">
-        <v>56884</v>
+        <v>56837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208255</v>
+        <v>206002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495647</v>
+        <v>495650</v>
       </c>
       <c r="R16" t="n">
-        <v>6719274</v>
+        <v>6719267</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,12 +2309,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,24 +2329,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111173602</t>
+          <t>https://artportalen.se/Sighting/127520634</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124240901</v>
+        <v>111173602</v>
       </c>
       <c r="B17" t="n">
         <v>56884</v>
@@ -2370,24 +2379,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495640</v>
+        <v>495647</v>
       </c>
       <c r="R17" t="n">
-        <v>6719238</v>
+        <v>6719274</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2411,17 +2421,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Skogsödlor har observerats på platsen under många år.</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,34 +2435,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Johan Liljeroos</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124240901</t>
+          <t>https://artportalen.se/Sighting/111173602</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134499476</v>
+        <v>124240901</v>
       </c>
       <c r="B18" t="n">
-        <v>56925</v>
+        <v>56884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,39 +2469,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495650</v>
+        <v>495640</v>
       </c>
       <c r="R18" t="n">
-        <v>6719267</v>
+        <v>6719238</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2524,22 +2532,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Skogsödlor har observerats på platsen under många år.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,6 +2551,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2559,22 +2563,22 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Johan Liljeroos</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134499476</t>
+          <t>https://artportalen.se/Sighting/124240901</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126387970</v>
+        <v>134499476</v>
       </c>
       <c r="B19" t="n">
-        <v>99035</v>
+        <v>56925</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,37 +2586,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>208260</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R19" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,12 +2645,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,16 +2686,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126387970</t>
+          <t>https://artportalen.se/Sighting/134499476</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134837603</v>
+        <v>126387970</v>
       </c>
       <c r="B20" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,24 +2721,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R20" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,22 +2757,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,16 +2788,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134837603</t>
+          <t>https://artportalen.se/Sighting/126387970</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134881502</v>
+        <v>134837603</v>
       </c>
       <c r="B21" t="n">
-        <v>99219</v>
+        <v>99112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2805,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,22 +2864,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,55 +2905,59 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134881502</t>
+          <t>https://artportalen.se/Sighting/134837603</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111126026</v>
+        <v>134881502</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>99219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495674</v>
+        <v>495654</v>
       </c>
       <c r="R22" t="n">
-        <v>6719224</v>
+        <v>6719285</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,27 +2981,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 blommande och drygt 40 bladrosetter</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,27 +3011,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111126026</t>
+          <t>https://artportalen.se/Sighting/134881502</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135252650</v>
+        <v>111126026</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3054,24 +3057,20 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gyllingen, Gyllingen, Dlr</t>
+          <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495788</v>
+        <v>495674</v>
       </c>
       <c r="R23" t="n">
-        <v>6719206</v>
+        <v>6719224</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3095,22 +3094,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 blommande och drygt 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,24 +3129,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252650</t>
+          <t>https://artportalen.se/Sighting/111126026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135323748</v>
+        <v>135252650</v>
       </c>
       <c r="B24" t="n">
         <v>99276</v>
@@ -3178,17 +3182,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Knärot Gyllingen, Dlr</t>
+          <t>Gyllingen, Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495693</v>
+        <v>495788</v>
       </c>
       <c r="R24" t="n">
-        <v>6719205</v>
+        <v>6719206</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3212,22 +3216,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3253,54 +3257,59 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135323748</t>
+          <t>https://artportalen.se/Sighting/135252650</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126387781</v>
+        <v>135323748</v>
       </c>
       <c r="B25" t="n">
-        <v>97983</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gyllingen, Dlr</t>
+          <t>Knärot Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495654</v>
+        <v>495693</v>
       </c>
       <c r="R25" t="n">
-        <v>6719285</v>
+        <v>6719205</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,12 +3333,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,6 +3373,108 @@
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323748</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126387781</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126387781</t>
         </is>
@@ -3385,6 +3506,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734963</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
